--- a/backend/templates/kp-v1.xlsx
+++ b/backend/templates/kp-v1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{642C39C5-9E48-7747-8243-334282081D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF94471-7FA2-A84C-B424-6D42BB425D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -236,7 +236,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -424,11 +424,42 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -468,13 +499,16 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -809,10 +843,10 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="16"/>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="23"/>
+      <c r="C2" s="25"/>
       <c r="D2" s="18"/>
       <c r="E2" s="18"/>
       <c r="F2" s="18"/>
@@ -821,10 +855,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="16"/>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="23"/>
+      <c r="C3" s="25"/>
       <c r="D3" s="18"/>
       <c r="E3" s="18"/>
       <c r="F3" s="18"/>
@@ -833,10 +867,10 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="16"/>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="25" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="18"/>
@@ -847,10 +881,10 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="16"/>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="25" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="18"/>
@@ -861,10 +895,10 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="16"/>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="25" t="s">
         <v>4</v>
       </c>
       <c r="D6" s="18"/>
@@ -914,7 +948,7 @@
     <row r="10" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="16"/>
       <c r="B10" s="7"/>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="24" t="s">
         <v>28</v>
       </c>
       <c r="D10" s="8" t="s">
@@ -932,7 +966,7 @@
     <row r="11" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="16"/>
       <c r="B11" s="7"/>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="24" t="s">
         <v>29</v>
       </c>
       <c r="D11" s="8" t="s">
@@ -973,17 +1007,17 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="16"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="22"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="28"/>
       <c r="H14" s="16"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="16"/>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="23" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="21"/>
@@ -1067,7 +1101,7 @@
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="16"/>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="23" t="s">
         <v>21</v>
       </c>
       <c r="C22" s="21"/>
@@ -1079,7 +1113,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="16"/>
-      <c r="B23" s="24" t="s">
+      <c r="B23" s="23" t="s">
         <v>22</v>
       </c>
       <c r="C23" s="21"/>
@@ -1091,7 +1125,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="16"/>
-      <c r="B24" s="24" t="s">
+      <c r="B24" s="23" t="s">
         <v>23</v>
       </c>
       <c r="C24" s="21"/>
@@ -1103,7 +1137,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="16"/>
-      <c r="B25" s="24" t="s">
+      <c r="B25" s="23" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="21"/>

--- a/backend/templates/kp-v1.xlsx
+++ b/backend/templates/kp-v1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF94471-7FA2-A84C-B424-6D42BB425D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0DCE5DB-F709-A940-9FEB-1A29F4C640B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -503,12 +503,12 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -823,7 +823,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="3" customWidth="1"/>
@@ -831,7 +831,7 @@
     <col min="7" max="7" width="3.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="16"/>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
@@ -841,36 +841,36 @@
       <c r="G1" s="16"/>
       <c r="H1" s="16"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="16"/>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="25"/>
+      <c r="C2" s="28"/>
       <c r="D2" s="18"/>
       <c r="E2" s="18"/>
       <c r="F2" s="18"/>
       <c r="G2" s="18"/>
       <c r="H2" s="16"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="16"/>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="25"/>
+      <c r="C3" s="28"/>
       <c r="D3" s="18"/>
       <c r="E3" s="18"/>
       <c r="F3" s="18"/>
       <c r="G3" s="18"/>
       <c r="H3" s="16"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="16"/>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="28" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="18"/>
@@ -879,12 +879,12 @@
       <c r="G4" s="18"/>
       <c r="H4" s="16"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="16"/>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="28" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="18"/>
@@ -893,12 +893,12 @@
       <c r="G5" s="18"/>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="16"/>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="28" t="s">
         <v>4</v>
       </c>
       <c r="D6" s="18"/>
@@ -907,7 +907,7 @@
       <c r="G6" s="18"/>
       <c r="H6" s="16"/>
     </row>
-    <row r="7" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="16"/>
       <c r="B7" s="20"/>
       <c r="C7" s="21"/>
@@ -917,7 +917,7 @@
       <c r="G7" s="22"/>
       <c r="H7" s="16"/>
     </row>
-    <row r="8" spans="1:8" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" s="7"/>
       <c r="C8" s="14"/>
@@ -927,7 +927,7 @@
       <c r="G8" s="10"/>
       <c r="H8" s="16"/>
     </row>
-    <row r="9" spans="1:8" s="1" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" s="1" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="17"/>
       <c r="B9" s="2"/>
       <c r="C9" s="3" t="s">
@@ -945,7 +945,7 @@
       <c r="G9" s="6"/>
       <c r="H9" s="17"/>
     </row>
-    <row r="10" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="16"/>
       <c r="B10" s="7"/>
       <c r="C10" s="24" t="s">
@@ -957,13 +957,17 @@
       <c r="E10" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="9" t="s">
-        <v>11</v>
+      <c r="F10" s="9" t="e">
+        <f>D10+E10</f>
+        <v>#VALUE!</v>
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="16"/>
-    </row>
-    <row r="11" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="16"/>
       <c r="B11" s="7"/>
       <c r="C11" s="24" t="s">
@@ -975,13 +979,17 @@
       <c r="E11" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F11" s="9" t="s">
-        <v>27</v>
+      <c r="F11" s="9" t="e">
+        <f>D11+E11</f>
+        <v>#VALUE!</v>
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="16"/>
-    </row>
-    <row r="12" spans="1:8" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="I11" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="7"/>
       <c r="C12" s="19"/>
@@ -995,7 +1003,7 @@
       <c r="G12" s="10"/>
       <c r="H12" s="16"/>
     </row>
-    <row r="13" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="16"/>
       <c r="B13" s="7"/>
       <c r="C13" s="15"/>
@@ -1005,17 +1013,17 @@
       <c r="G13" s="10"/>
       <c r="H13" s="16"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="16"/>
-      <c r="B14" s="26"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="28"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="27"/>
       <c r="H14" s="16"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="16"/>
       <c r="B15" s="23" t="s">
         <v>14</v>
@@ -1027,7 +1035,7 @@
       <c r="G15" s="22"/>
       <c r="H15" s="16"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="16"/>
       <c r="B16" s="20" t="s">
         <v>15</v>

--- a/backend/templates/kp-v1.xlsx
+++ b/backend/templates/kp-v1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0DCE5DB-F709-A940-9FEB-1A29F4C640B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23663871-3218-624D-AF11-E621B5E03B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -823,7 +823,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="3" customWidth="1"/>
@@ -831,7 +831,7 @@
     <col min="7" max="7" width="3.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="16"/>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
@@ -841,7 +841,7 @@
       <c r="G1" s="16"/>
       <c r="H1" s="16"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="16"/>
       <c r="B2" s="28" t="s">
         <v>0</v>
@@ -853,7 +853,7 @@
       <c r="G2" s="18"/>
       <c r="H2" s="16"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="16"/>
       <c r="B3" s="28" t="s">
         <v>1</v>
@@ -865,7 +865,7 @@
       <c r="G3" s="18"/>
       <c r="H3" s="16"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="16"/>
       <c r="B4" s="28" t="s">
         <v>2</v>
@@ -879,7 +879,7 @@
       <c r="G4" s="18"/>
       <c r="H4" s="16"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="16"/>
       <c r="B5" s="28" t="s">
         <v>3</v>
@@ -893,7 +893,7 @@
       <c r="G5" s="18"/>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="16"/>
       <c r="B6" s="28" t="s">
         <v>4</v>
@@ -907,7 +907,7 @@
       <c r="G6" s="18"/>
       <c r="H6" s="16"/>
     </row>
-    <row r="7" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="16"/>
       <c r="B7" s="20"/>
       <c r="C7" s="21"/>
@@ -917,7 +917,7 @@
       <c r="G7" s="22"/>
       <c r="H7" s="16"/>
     </row>
-    <row r="8" spans="1:9" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" s="7"/>
       <c r="C8" s="14"/>
@@ -927,7 +927,7 @@
       <c r="G8" s="10"/>
       <c r="H8" s="16"/>
     </row>
-    <row r="9" spans="1:9" s="1" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" s="1" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="17"/>
       <c r="B9" s="2"/>
       <c r="C9" s="3" t="s">
@@ -945,7 +945,7 @@
       <c r="G9" s="6"/>
       <c r="H9" s="17"/>
     </row>
-    <row r="10" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="16"/>
       <c r="B10" s="7"/>
       <c r="C10" s="24" t="s">
@@ -957,17 +957,13 @@
       <c r="E10" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="9" t="e">
-        <f>D10+E10</f>
-        <v>#VALUE!</v>
+      <c r="F10" s="9" t="s">
+        <v>11</v>
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="16"/>
-      <c r="I10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="16"/>
       <c r="B11" s="7"/>
       <c r="C11" s="24" t="s">
@@ -979,17 +975,13 @@
       <c r="E11" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F11" s="9" t="e">
-        <f>D11+E11</f>
-        <v>#VALUE!</v>
+      <c r="F11" s="9" t="s">
+        <v>27</v>
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="16"/>
-      <c r="I11" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:8" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="7"/>
       <c r="C12" s="19"/>
@@ -1003,7 +995,7 @@
       <c r="G12" s="10"/>
       <c r="H12" s="16"/>
     </row>
-    <row r="13" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="16"/>
       <c r="B13" s="7"/>
       <c r="C13" s="15"/>
@@ -1013,7 +1005,7 @@
       <c r="G13" s="10"/>
       <c r="H13" s="16"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="16"/>
       <c r="B14" s="25"/>
       <c r="C14" s="26"/>
@@ -1023,7 +1015,7 @@
       <c r="G14" s="27"/>
       <c r="H14" s="16"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="16"/>
       <c r="B15" s="23" t="s">
         <v>14</v>
@@ -1035,7 +1027,7 @@
       <c r="G15" s="22"/>
       <c r="H15" s="16"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="16"/>
       <c r="B16" s="20" t="s">
         <v>15</v>

--- a/backend/templates/kp-v1.xlsx
+++ b/backend/templates/kp-v1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23663871-3218-624D-AF11-E621B5E03B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACB5D23E-80ED-704C-9BBA-D9402290B4B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -459,7 +459,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -507,6 +507,18 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1017,10 +1029,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="16"/>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="21"/>
+      <c r="C15" s="30"/>
       <c r="D15" s="21"/>
       <c r="E15" s="21"/>
       <c r="F15" s="21"/>
@@ -1029,10 +1041,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="16"/>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="21"/>
+      <c r="C16" s="32"/>
       <c r="D16" s="21"/>
       <c r="E16" s="21"/>
       <c r="F16" s="21"/>
@@ -1158,7 +1170,9 @@
       <c r="H26" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>

--- a/backend/templates/kp-v1.xlsx
+++ b/backend/templates/kp-v1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACB5D23E-80ED-704C-9BBA-D9402290B4B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D376B99-975F-C045-AA71-37A434BBFE9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -236,7 +236,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -248,13 +248,19 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
@@ -272,7 +278,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="medium">
@@ -281,30 +287,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -425,7 +407,58 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right/>
@@ -437,21 +470,23 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -459,12 +494,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -473,53 +508,73 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -844,333 +899,337 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="16"/>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
+      <c r="A1" s="10"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="16"/>
-      <c r="B2" s="28" t="s">
+      <c r="A2" s="10"/>
+      <c r="B2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="16"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="10"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="16"/>
-      <c r="B3" s="28" t="s">
+      <c r="A3" s="10"/>
+      <c r="B3" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="28"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="16"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="10"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="16"/>
-      <c r="B4" s="28" t="s">
+      <c r="A4" s="10"/>
+      <c r="B4" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="16"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="10"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="16"/>
-      <c r="B5" s="28" t="s">
+      <c r="A5" s="10"/>
+      <c r="B5" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="16"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="10"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="16"/>
-      <c r="B6" s="28" t="s">
+      <c r="A6" s="10"/>
+      <c r="B6" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="16"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="10"/>
     </row>
     <row r="7" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="16"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="16"/>
+      <c r="A7" s="10"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="10"/>
     </row>
     <row r="8" spans="1:8" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="16"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="16"/>
+      <c r="A8" s="10"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="10"/>
     </row>
     <row r="9" spans="1:8" s="1" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="17"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="3" t="s">
+      <c r="A9" s="11"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G9" s="6"/>
-      <c r="H9" s="17"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="11"/>
     </row>
     <row r="10" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="16"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="24" t="s">
+      <c r="A10" s="10"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="16"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="10"/>
     </row>
     <row r="11" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="16"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="24" t="s">
+      <c r="A11" s="10"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="16"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="10"/>
     </row>
     <row r="12" spans="1:8" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="16"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="12" t="s">
+      <c r="A12" s="10"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G12" s="10"/>
-      <c r="H12" s="16"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="10"/>
     </row>
     <row r="13" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="16"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="16"/>
+      <c r="A13" s="10"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="10"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="16"/>
-      <c r="B14" s="25"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="16"/>
+      <c r="A14" s="10"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="10"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="16"/>
-      <c r="B15" s="29" t="s">
+      <c r="A15" s="10"/>
+      <c r="B15" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="30"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="16"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="10"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="16"/>
-      <c r="B16" s="31" t="s">
+      <c r="A16" s="10"/>
+      <c r="B16" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="16"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="10"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="16"/>
-      <c r="B17" s="20" t="s">
+      <c r="A17" s="10"/>
+      <c r="B17" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="16"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="10"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="16"/>
-      <c r="B18" s="20" t="s">
+      <c r="A18" s="10"/>
+      <c r="B18" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="16"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="10"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="16"/>
+      <c r="A19" s="10"/>
       <c r="B19" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="16"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="10"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="16"/>
+      <c r="A20" s="10"/>
       <c r="B20" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="16"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="10"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="16"/>
+      <c r="A21" s="10"/>
       <c r="B21" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="16"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="10"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="16"/>
-      <c r="B22" s="23" t="s">
+      <c r="A22" s="10"/>
+      <c r="B22" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="16"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="10"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="16"/>
-      <c r="B23" s="23" t="s">
+      <c r="A23" s="10"/>
+      <c r="B23" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="16"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="10"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="16"/>
-      <c r="B24" s="23" t="s">
+      <c r="A24" s="10"/>
+      <c r="B24" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="16"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="10"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="16"/>
-      <c r="B25" s="23" t="s">
+      <c r="A25" s="10"/>
+      <c r="B25" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="16"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="10"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="16"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="16">
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B2:C2"/>
@@ -1178,6 +1237,11 @@
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="G9:G12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>

--- a/backend/templates/kp-v1.xlsx
+++ b/backend/templates/kp-v1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D376B99-975F-C045-AA71-37A434BBFE9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB505F1-37D6-8B45-81D4-BCAC3C43F129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -236,7 +236,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -248,6 +248,15 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -287,6 +296,15 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -427,17 +445,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -447,43 +454,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top/>
@@ -494,87 +475,77 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -910,93 +881,93 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="10"/>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
       <c r="H2" s="10"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="10"/>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="25"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
       <c r="H3" s="10"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="10"/>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
       <c r="H4" s="10"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="10"/>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
       <c r="H5" s="10"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="10"/>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
       <c r="H6" s="10"/>
     </row>
     <row r="7" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10"/>
-      <c r="B7" s="26"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="15"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="14"/>
       <c r="H7" s="10"/>
     </row>
     <row r="8" spans="1:8" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10"/>
-      <c r="B8" s="31"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="10"/>
+      <c r="A8" s="31"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="29"/>
     </row>
     <row r="9" spans="1:8" s="1" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="11"/>
-      <c r="B9" s="34"/>
+      <c r="A9" s="32"/>
+      <c r="B9" s="28"/>
       <c r="C9" s="2" t="s">
         <v>5</v>
       </c>
@@ -1009,13 +980,13 @@
       <c r="F9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G9" s="34"/>
-      <c r="H9" s="11"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="30"/>
     </row>
     <row r="10" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="10"/>
-      <c r="B10" s="34"/>
-      <c r="C10" s="16" t="s">
+      <c r="A10" s="31"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="15" t="s">
         <v>28</v>
       </c>
       <c r="D10" s="5" t="s">
@@ -1027,13 +998,13 @@
       <c r="F10" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="34"/>
-      <c r="H10" s="10"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="29"/>
     </row>
     <row r="11" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="10"/>
-      <c r="B11" s="34"/>
-      <c r="C11" s="16" t="s">
+      <c r="A11" s="31"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="15" t="s">
         <v>29</v>
       </c>
       <c r="D11" s="5" t="s">
@@ -1045,13 +1016,13 @@
       <c r="F11" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="34"/>
-      <c r="H11" s="10"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="29"/>
     </row>
     <row r="12" spans="1:8" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10"/>
-      <c r="B12" s="34"/>
-      <c r="C12" s="13"/>
+      <c r="A12" s="31"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="12"/>
       <c r="D12" s="7"/>
       <c r="E12" s="8" t="s">
         <v>12</v>
@@ -1059,75 +1030,75 @@
       <c r="F12" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G12" s="34"/>
-      <c r="H12" s="10"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="29"/>
     </row>
     <row r="13" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="10"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="10"/>
+      <c r="A13" s="31"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="29"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="10"/>
-      <c r="B14" s="26"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="18"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="17"/>
       <c r="H14" s="10"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="10"/>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="15"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="14"/>
       <c r="H15" s="10"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="10"/>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="24"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="15"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="14"/>
       <c r="H16" s="10"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="10"/>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="24"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="15"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="14"/>
       <c r="H17" s="10"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="10"/>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="24"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="15"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="14"/>
       <c r="H18" s="10"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -1135,11 +1106,11 @@
       <c r="B19" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="15"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="14"/>
       <c r="H19" s="10"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
@@ -1147,11 +1118,11 @@
       <c r="B20" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="15"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="14"/>
       <c r="H20" s="10"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
@@ -1159,59 +1130,59 @@
       <c r="B21" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="15"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="14"/>
       <c r="H21" s="10"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="10"/>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="22"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="15"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="14"/>
       <c r="H22" s="10"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="10"/>
-      <c r="B23" s="19" t="s">
+      <c r="B23" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="15"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="14"/>
       <c r="H23" s="10"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="10"/>
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="15"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="14"/>
       <c r="H24" s="10"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="10"/>
-      <c r="B25" s="19" t="s">
+      <c r="B25" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="15"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="14"/>
       <c r="H25" s="10"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
@@ -1225,11 +1196,17 @@
       <c r="H26" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="22">
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B20:C20"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B19:C19"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B2:C2"/>

--- a/backend/templates/kp-v1.xlsx
+++ b/backend/templates/kp-v1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB505F1-37D6-8B45-81D4-BCAC3C43F129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8884377B-CDE4-BE4B-9B16-F3CDF50E6251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -236,7 +236,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -245,144 +245,132 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -395,79 +383,6 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -475,78 +390,77 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -870,338 +784,343 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="10"/>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="10"/>
-      <c r="B2" s="22" t="s">
+      <c r="A2" s="3"/>
+      <c r="B2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="10"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="3"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="10"/>
-      <c r="B3" s="22" t="s">
+      <c r="A3" s="3"/>
+      <c r="B3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="10"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="10"/>
-      <c r="B4" s="22" t="s">
+      <c r="A4" s="3"/>
+      <c r="B4" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="10"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="10"/>
-      <c r="B5" s="22" t="s">
+      <c r="A5" s="3"/>
+      <c r="B5" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="10"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="10"/>
-      <c r="B6" s="22" t="s">
+      <c r="A6" s="3"/>
+      <c r="B6" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="10"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="10"/>
-      <c r="B7" s="23"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="10"/>
-    </row>
-    <row r="8" spans="1:8" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="31"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="29"/>
+      <c r="A7" s="3"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="16"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="16"/>
     </row>
     <row r="9" spans="1:8" s="1" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="32"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="2" t="s">
+      <c r="A9" s="17"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="G9" s="27"/>
-      <c r="H9" s="30"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="17"/>
     </row>
     <row r="10" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="31"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="15" t="s">
+      <c r="A10" s="16"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="27"/>
-      <c r="H10" s="29"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="16"/>
     </row>
     <row r="11" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="31"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="15" t="s">
+      <c r="A11" s="16"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="27"/>
-      <c r="H11" s="29"/>
-    </row>
-    <row r="12" spans="1:8" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="31"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="8" t="s">
+      <c r="G11" s="20"/>
+      <c r="H11" s="16"/>
+    </row>
+    <row r="12" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="16"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="G12" s="27"/>
-      <c r="H12" s="29"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="16"/>
     </row>
     <row r="13" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="31"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
+      <c r="A13" s="16"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
       <c r="G13" s="25"/>
-      <c r="H13" s="29"/>
+      <c r="H13" s="16"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="10"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="10"/>
+      <c r="A14" s="3"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="3"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="10"/>
-      <c r="B15" s="18" t="s">
+      <c r="A15" s="3"/>
+      <c r="B15" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="3"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="10"/>
-      <c r="B16" s="20" t="s">
+      <c r="A16" s="3"/>
+      <c r="B16" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="10"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="3"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="10"/>
-      <c r="B17" s="20" t="s">
+      <c r="A17" s="3"/>
+      <c r="B17" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="21"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="10"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="3"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="10"/>
-      <c r="B18" s="20" t="s">
+      <c r="A18" s="3"/>
+      <c r="B18" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="21"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="10"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="3"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="10"/>
-      <c r="B19" s="20" t="s">
+      <c r="A19" s="3"/>
+      <c r="B19" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="21"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="10"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="3"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="10"/>
-      <c r="B20" s="20" t="s">
+      <c r="A20" s="3"/>
+      <c r="B20" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="21"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="10"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="3"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="10"/>
-      <c r="B21" s="20" t="s">
+      <c r="A21" s="3"/>
+      <c r="B21" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="21"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="10"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="3"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="10"/>
-      <c r="B22" s="18" t="s">
+      <c r="A22" s="3"/>
+      <c r="B22" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="19"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="3"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="10"/>
-      <c r="B23" s="18" t="s">
+      <c r="A23" s="3"/>
+      <c r="B23" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="19"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="3"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="10"/>
-      <c r="B24" s="18" t="s">
+      <c r="A24" s="3"/>
+      <c r="B24" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="19"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="3"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="10"/>
-      <c r="B25" s="18" t="s">
+      <c r="A25" s="3"/>
+      <c r="B25" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="19"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="3"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="G9:G12"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B22:C22"/>
@@ -1209,16 +1128,11 @@
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="G9:G12"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B20:C20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
